--- a/models/CRWV.xlsx
+++ b/models/CRWV.xlsx
@@ -36,9 +36,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0.00##"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -55,10 +56,13 @@
       <color rgb="000000FF"/>
     </font>
     <font>
-      <color rgb="00008000"/>
+      <color rgb="00595959"/>
     </font>
     <font>
       <color rgb="00000000"/>
+    </font>
+    <font>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
@@ -66,9 +70,6 @@
     </font>
     <font>
       <i val="1"/>
-    </font>
-    <font>
-      <color rgb="00595959"/>
     </font>
     <font>
       <i val="1"/>
@@ -100,18 +101,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -121,7 +122,11 @@
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -747,7 +752,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[derived; proposed] Technology equipment, gross 9,146,575 thousand divided by more than 250,000 GPUs at Dec 31, 2024. A fleet average that includes servers and networking and excludes construction in progress. Newer GPU generations cost more than this average.</t>
+          <t>[derived; proposed] Technology equipment, gross 9,146,575 thousand divided by more than 250,000 GPUs at Dec 31, 2024. A fleet average that includes servers and networking and excludes construction in progress. Compare with the model's capex per MW added (Outputs sheet), which is the same idea measured from cash flows.</t>
         </is>
       </c>
     </row>
@@ -772,7 +777,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>[derived; proposed] More than 360 MW of active power divided by more than 250,000 GPUs at Dec 31, 2024. Facility-level power per GPU, so cooling and non-GPU load are already inside it.</t>
+          <t>[derived; proposed] More than 360 MW of active power divided by more than 250,000 GPUs at Dec 31, 2024. Facility-level power per GPU, so cooling and non-GPU load are already inside it. This is the ONE assumption that converts disclosed MW into GPU counts; every per-GPU line scales with it, the per-MW lines do not use it.</t>
         </is>
       </c>
     </row>
@@ -835,7 +840,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>[judgment; proposed] Set to 1.0 because price_per_gpu_hour below is revenue per INSTALLED hour. Idle and not-yet-billing GPUs are already inside that price.</t>
+          <t>[judgment; proposed] Set to 1.0 because the model measures revenue per INSTALLED GPU-hour (quarterly revenue over average installed capacity). Idle and not-yet-billing GPUs are already inside that figure. Only used by the per-GPU lines.</t>
         </is>
       </c>
     </row>
@@ -938,21 +943,17 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1.354</v>
+        <v>0</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>USD/GPU-hour</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>S-1 p.113, p.2</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>[derived; proposed] Q4 2024 revenue 747,430 thousand divided by 250,000 GPUs times 2,208 hours. Realised revenue per installed GPU-hour across the whole fleet. It is NOT a contract price, and it is understated because the year-end GPU count is applied to the whole quarter.</t>
+          <t>[judgment; proposed] Not used: the model computes revenue per installed GPU-hour for each quarter from reported revenue and disclosed capacity (see the Outputs sheet). Kept at 0 so the engine's rental mode has a defined input.</t>
         </is>
       </c>
     </row>
@@ -984,21 +985,17 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0.4734</v>
+        <v>0</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>USD/GPU-hour</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>S-1 p.113, p.115, p.2</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[derived; proposed] Q4 2024 revenue less adjusted EBITDA (747,430 less 486,114 thousand) per installed GPU-hour. Lumps energy, data-centre leases, staff and everything else above adjusted EBITDA into one number.</t>
+          <t>[judgment; proposed] Not used: each quarter's cash cost per GPU-hour is revenue less adjusted EBITDA over installed GPU-hours, computed by the model. Kept at 0.</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1077,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1101,135 +1103,490 @@
       </c>
       <c r="C1" s="13" t="inlineStr">
         <is>
-          <t>2024Q4</t>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>2025Q4</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Active power, end of quarter</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="n">
+        <v>420</v>
+      </c>
+      <c r="D2" s="14" t="n">
+        <v>470</v>
+      </c>
+      <c r="E2" s="14" t="n">
+        <v>590</v>
+      </c>
+      <c r="F2" s="14" t="n">
+        <v>850</v>
+      </c>
+      <c r="G2" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H2" s="14" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Active power added</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D3" s="15">
+        <f>D2-C2</f>
+        <v/>
+      </c>
+      <c r="E3" s="15">
+        <f>E2-D2</f>
+        <v/>
+      </c>
+      <c r="F3" s="15">
+        <f>F2-E2</f>
+        <v/>
+      </c>
+      <c r="G3" s="15">
+        <f>G2-F2</f>
+        <v/>
+      </c>
+      <c r="H3" s="15">
+        <f>H2-G2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Active power, average</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>390</v>
+      </c>
+      <c r="D4" s="15">
+        <f>(C2+D2)/2</f>
+        <v/>
+      </c>
+      <c r="E4" s="15">
+        <f>(D2+E2)/2</f>
+        <v/>
+      </c>
+      <c r="F4" s="15">
+        <f>(E2+F2)/2</f>
+        <v/>
+      </c>
+      <c r="G4" s="15">
+        <f>(F2+G2)/2</f>
+        <v/>
+      </c>
+      <c r="H4" s="15">
+        <f>(G2+H2)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Contracted power</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GW</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Revenue backlog</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>USD bn</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Hours in the quarter</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>hours</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>2160</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>2184</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>2208</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>2208</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>2160</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GPUs installed, average (from MW and kW per GPU)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GPUs</t>
+        </is>
+      </c>
+      <c r="C8" s="17">
+        <f>C4*1000/in_power_draw_kw</f>
+        <v/>
+      </c>
+      <c r="D8" s="17">
+        <f>D4*1000/in_power_draw_kw</f>
+        <v/>
+      </c>
+      <c r="E8" s="17">
+        <f>E4*1000/in_power_draw_kw</f>
+        <v/>
+      </c>
+      <c r="F8" s="17">
+        <f>F4*1000/in_power_draw_kw</f>
+        <v/>
+      </c>
+      <c r="G8" s="17">
+        <f>G4*1000/in_power_draw_kw</f>
+        <v/>
+      </c>
+      <c r="H8" s="17">
+        <f>H4*1000/in_power_draw_kw</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Installed GPU-hours</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>millions</t>
+        </is>
+      </c>
+      <c r="C9" s="15">
+        <f>C8*C7/1000000</f>
+        <v/>
+      </c>
+      <c r="D9" s="15">
+        <f>D8*D7/1000000</f>
+        <v/>
+      </c>
+      <c r="E9" s="15">
+        <f>E8*E7/1000000</f>
+        <v/>
+      </c>
+      <c r="F9" s="15">
+        <f>F8*F7/1000000</f>
+        <v/>
+      </c>
+      <c r="G9" s="15">
+        <f>G8*G7/1000000</f>
+        <v/>
+      </c>
+      <c r="H9" s="15">
+        <f>H8*H7/1000000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>USD m</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>982</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>1212</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>1364.676</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>1571.904</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>2078</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Adjusted EBITDA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>USD m</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>606.131</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>753.169</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>838.124</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>898</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>1157</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capital expenditure</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>USD m</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>1407</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>2453</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>2389.239</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>4059.761</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>7695</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>6422</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Capital expenditure, cumulative</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>USD m</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>1407</v>
+      </c>
+      <c r="D13" s="18">
+        <f>C13+D12</f>
+        <v/>
+      </c>
+      <c r="E13" s="18">
+        <f>D13+E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="18">
+        <f>E13+F12</f>
+        <v/>
+      </c>
+      <c r="G13" s="18">
+        <f>F13+G12</f>
+        <v/>
+      </c>
+      <c r="H13" s="18">
+        <f>G13+H12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Active power added, cumulative</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D14" s="15">
+        <f>C14+D3</f>
+        <v/>
+      </c>
+      <c r="E14" s="15">
+        <f>D14+E3</f>
+        <v/>
+      </c>
+      <c r="F14" s="15">
+        <f>E14+F3</f>
+        <v/>
+      </c>
+      <c r="G14" s="15">
+        <f>F14+G3</f>
+        <v/>
+      </c>
+      <c r="H14" s="15">
+        <f>G14+H3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Capital recovery factor (share of price due each year)</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="C2" s="14">
+      <c r="C15" s="17">
         <f>IF(in_financing_rate=0,1/in_depreciation_years,in_financing_rate/(1-(1+in_financing_rate)^-in_depreciation_years))</f>
         <v/>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Capital charge</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>USD/GPU-hour</t>
-        </is>
-      </c>
-      <c r="C3" s="14">
-        <f>in_chip_cost*(1-in_residual_value_share/(1+in_financing_rate)^in_depreciation_years)*C2/8760</f>
+      <c r="D15" s="17">
+        <f>IF(in_financing_rate=0,1/in_depreciation_years,in_financing_rate/(1-(1+in_financing_rate)^-in_depreciation_years))</f>
         <v/>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>USD/GPU-hour</t>
-        </is>
-      </c>
-      <c r="C4" s="14">
-        <f>in_power_draw_kw*in_pue*in_electricity_price_kwh*(in_utilization+(1-in_utilization)*in_idle_power_share)</f>
+      <c r="E15" s="17">
+        <f>IF(in_financing_rate=0,1/in_depreciation_years,in_financing_rate/(1-(1+in_financing_rate)^-in_depreciation_years))</f>
         <v/>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Data-centre space</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>USD/GPU-hour</t>
-        </is>
-      </c>
-      <c r="C5" s="14">
-        <f>in_facility_cost_per_kw_month*in_power_draw_kw*12/8760</f>
+      <c r="F15" s="17">
+        <f>IF(in_financing_rate=0,1/in_depreciation_years,in_financing_rate/(1-(1+in_financing_rate)^-in_depreciation_years))</f>
         <v/>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Other operating cost</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>USD/GPU-hour</t>
-        </is>
-      </c>
-      <c r="C6" s="14">
-        <f>in_other_opex_per_gpu_hour</f>
+      <c r="G15" s="17">
+        <f>IF(in_financing_rate=0,1/in_depreciation_years,in_financing_rate/(1-(1+in_financing_rate)^-in_depreciation_years))</f>
         <v/>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cash cost</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>USD/GPU-hour</t>
-        </is>
-      </c>
-      <c r="C7" s="15">
-        <f>C4+C5+C6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Fully loaded cost</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>USD/GPU-hour</t>
-        </is>
-      </c>
-      <c r="C8" s="15">
-        <f>C7+C3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>USD/GPU-hour</t>
-        </is>
-      </c>
-      <c r="C9" s="14">
-        <f>in_price_per_gpu_hour*in_utilization</f>
+      <c r="H15" s="17">
+        <f>IF(in_financing_rate=0,1/in_depreciation_years,in_financing_rate/(1-(1+in_financing_rate)^-in_depreciation_years))</f>
         <v/>
       </c>
     </row>
@@ -1244,12 +1601,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1265,78 +1627,183 @@
       </c>
       <c r="C1" s="13" t="inlineStr">
         <is>
-          <t>2024Q4</t>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>2025Q4</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cash margin</t>
+          <t>Revenue per MW, annualised</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>USD/GPU-hour</t>
-        </is>
-      </c>
-      <c r="C2" s="14">
-        <f>Drivers!C9-Drivers!C7</f>
+          <t>USD m</t>
+        </is>
+      </c>
+      <c r="C2" s="19">
+        <f>Drivers!C10*4/Drivers!C4</f>
+        <v/>
+      </c>
+      <c r="D2" s="19">
+        <f>Drivers!D10*4/Drivers!D4</f>
+        <v/>
+      </c>
+      <c r="E2" s="19">
+        <f>Drivers!E10*4/Drivers!E4</f>
+        <v/>
+      </c>
+      <c r="F2" s="19">
+        <f>Drivers!F10*4/Drivers!F4</f>
+        <v/>
+      </c>
+      <c r="G2" s="19">
+        <f>Drivers!G10*4/Drivers!G4</f>
+        <v/>
+      </c>
+      <c r="H2" s="19">
+        <f>Drivers!H10*4/Drivers!H4</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cash margin, share of revenue</t>
+          <t>Adjusted EBITDA per MW, annualised</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="C3" s="16">
-        <f>C2/Drivers!C9</f>
+          <t>USD m</t>
+        </is>
+      </c>
+      <c r="C3" s="19">
+        <f>Drivers!C11*4/Drivers!C4</f>
+        <v/>
+      </c>
+      <c r="D3" s="19">
+        <f>Drivers!D11*4/Drivers!D4</f>
+        <v/>
+      </c>
+      <c r="E3" s="19">
+        <f>Drivers!E11*4/Drivers!E4</f>
+        <v/>
+      </c>
+      <c r="F3" s="19">
+        <f>Drivers!F11*4/Drivers!F4</f>
+        <v/>
+      </c>
+      <c r="G3" s="19">
+        <f>Drivers!G11*4/Drivers!G4</f>
+        <v/>
+      </c>
+      <c r="H3" s="19">
+        <f>Drivers!H11*4/Drivers!H4</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Fully loaded margin</t>
+          <t>Adjusted EBITDA margin</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>USD/GPU-hour</t>
-        </is>
-      </c>
-      <c r="C4" s="14">
-        <f>Drivers!C9-Drivers!C8</f>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C4" s="20">
+        <f>Drivers!C11/Drivers!C10</f>
+        <v/>
+      </c>
+      <c r="D4" s="20">
+        <f>Drivers!D11/Drivers!D10</f>
+        <v/>
+      </c>
+      <c r="E4" s="20">
+        <f>Drivers!E11/Drivers!E10</f>
+        <v/>
+      </c>
+      <c r="F4" s="20">
+        <f>Drivers!F11/Drivers!F10</f>
+        <v/>
+      </c>
+      <c r="G4" s="20">
+        <f>Drivers!G11/Drivers!G10</f>
+        <v/>
+      </c>
+      <c r="H4" s="20">
+        <f>Drivers!H11/Drivers!H10</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Break-even rental price</t>
+          <t>Capex per MW added, cumulative since the first quarter</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>USD/GPU-hour</t>
-        </is>
-      </c>
-      <c r="C5" s="14">
-        <f>Drivers!C8/in_utilization</f>
+          <t>USD m</t>
+        </is>
+      </c>
+      <c r="C5" s="19">
+        <f>Drivers!C13/Drivers!C14</f>
+        <v/>
+      </c>
+      <c r="D5" s="19">
+        <f>Drivers!D13/Drivers!D14</f>
+        <v/>
+      </c>
+      <c r="E5" s="19">
+        <f>Drivers!E13/Drivers!E14</f>
+        <v/>
+      </c>
+      <c r="F5" s="19">
+        <f>Drivers!F13/Drivers!F14</f>
+        <v/>
+      </c>
+      <c r="G5" s="19">
+        <f>Drivers!G13/Drivers!G14</f>
+        <v/>
+      </c>
+      <c r="H5" s="19">
+        <f>Drivers!H13/Drivers!H14</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Payback, model</t>
+          <t>Payback per MW: capex per MW / EBITDA per MW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1344,40 +1811,316 @@
           <t>years</t>
         </is>
       </c>
-      <c r="C6" s="14">
-        <f>IF(C2&gt;0,in_chip_cost/(C2*8760),"never")</f>
+      <c r="C6" s="15">
+        <f>C5/C3</f>
+        <v/>
+      </c>
+      <c r="D6" s="15">
+        <f>D5/D3</f>
+        <v/>
+      </c>
+      <c r="E6" s="15">
+        <f>E5/E3</f>
+        <v/>
+      </c>
+      <c r="F6" s="15">
+        <f>F5/F3</f>
+        <v/>
+      </c>
+      <c r="G6" s="15">
+        <f>G5/G3</f>
+        <v/>
+      </c>
+      <c r="H6" s="15">
+        <f>H5/H3</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Backlog, years of current revenue</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="C7" s="17">
+        <f>Drivers!C6*1000/(Drivers!C10*4)</f>
+        <v/>
+      </c>
+      <c r="D7" s="17">
+        <f>Drivers!D6*1000/(Drivers!D10*4)</f>
+        <v/>
+      </c>
+      <c r="E7" s="17">
+        <f>Drivers!E6*1000/(Drivers!E10*4)</f>
+        <v/>
+      </c>
+      <c r="F7" s="17">
+        <f>Drivers!F6*1000/(Drivers!F10*4)</f>
+        <v/>
+      </c>
+      <c r="G7" s="17">
+        <f>Drivers!G6*1000/(Drivers!G10*4)</f>
+        <v/>
+      </c>
+      <c r="H7" s="17">
+        <f>Drivers!H6*1000/(Drivers!H10*4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Revenue per installed GPU-hour</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>USD/GPU-hour</t>
+        </is>
+      </c>
+      <c r="C8" s="17">
+        <f>Drivers!C10/Drivers!C9</f>
+        <v/>
+      </c>
+      <c r="D8" s="17">
+        <f>Drivers!D10/Drivers!D9</f>
+        <v/>
+      </c>
+      <c r="E8" s="17">
+        <f>Drivers!E10/Drivers!E9</f>
+        <v/>
+      </c>
+      <c r="F8" s="17">
+        <f>Drivers!F10/Drivers!F9</f>
+        <v/>
+      </c>
+      <c r="G8" s="17">
+        <f>Drivers!G10/Drivers!G9</f>
+        <v/>
+      </c>
+      <c r="H8" s="17">
+        <f>Drivers!H10/Drivers!H9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cash cost per installed GPU-hour</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>USD/GPU-hour</t>
+        </is>
+      </c>
+      <c r="C9" s="17">
+        <f>(Drivers!C10-Drivers!C11)/Drivers!C9</f>
+        <v/>
+      </c>
+      <c r="D9" s="17">
+        <f>(Drivers!D10-Drivers!D11)/Drivers!D9</f>
+        <v/>
+      </c>
+      <c r="E9" s="17">
+        <f>(Drivers!E10-Drivers!E11)/Drivers!E9</f>
+        <v/>
+      </c>
+      <c r="F9" s="17">
+        <f>(Drivers!F10-Drivers!F11)/Drivers!F9</f>
+        <v/>
+      </c>
+      <c r="G9" s="17">
+        <f>(Drivers!G10-Drivers!G11)/Drivers!G9</f>
+        <v/>
+      </c>
+      <c r="H9" s="17">
+        <f>(Drivers!H10-Drivers!H11)/Drivers!H9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cash margin per installed GPU-hour</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>USD/GPU-hour</t>
+        </is>
+      </c>
+      <c r="C10" s="15">
+        <f>C8-C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="15">
+        <f>D8-D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="15">
+        <f>E8-E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="15">
+        <f>F8-F9</f>
+        <v/>
+      </c>
+      <c r="G10" s="15">
+        <f>G8-G9</f>
+        <v/>
+      </c>
+      <c r="H10" s="15">
+        <f>H8-H9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capital charge per installed GPU-hour</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>USD/GPU-hour</t>
+        </is>
+      </c>
+      <c r="C11" s="17">
+        <f>in_chip_cost*(1-in_residual_value_share/(1+in_financing_rate)^in_depreciation_years)*Drivers!C15/8760</f>
+        <v/>
+      </c>
+      <c r="D11" s="17">
+        <f>in_chip_cost*(1-in_residual_value_share/(1+in_financing_rate)^in_depreciation_years)*Drivers!D15/8760</f>
+        <v/>
+      </c>
+      <c r="E11" s="17">
+        <f>in_chip_cost*(1-in_residual_value_share/(1+in_financing_rate)^in_depreciation_years)*Drivers!E15/8760</f>
+        <v/>
+      </c>
+      <c r="F11" s="17">
+        <f>in_chip_cost*(1-in_residual_value_share/(1+in_financing_rate)^in_depreciation_years)*Drivers!F15/8760</f>
+        <v/>
+      </c>
+      <c r="G11" s="17">
+        <f>in_chip_cost*(1-in_residual_value_share/(1+in_financing_rate)^in_depreciation_years)*Drivers!G15/8760</f>
+        <v/>
+      </c>
+      <c r="H11" s="17">
+        <f>in_chip_cost*(1-in_residual_value_share/(1+in_financing_rate)^in_depreciation_years)*Drivers!H15/8760</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fully loaded margin per installed GPU-hour</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>USD/GPU-hour</t>
+        </is>
+      </c>
+      <c r="C12" s="15">
+        <f>C10-C11</f>
+        <v/>
+      </c>
+      <c r="D12" s="15">
+        <f>D10-D11</f>
+        <v/>
+      </c>
+      <c r="E12" s="15">
+        <f>E10-E11</f>
+        <v/>
+      </c>
+      <c r="F12" s="15">
+        <f>F10-F11</f>
+        <v/>
+      </c>
+      <c r="G12" s="15">
+        <f>G10-G11</f>
+        <v/>
+      </c>
+      <c r="H12" s="15">
+        <f>H10-H11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Payback per GPU (engine)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="C13" s="17">
+        <f>IF(C10&gt;0,in_chip_cost/(C10*8760),"never")</f>
+        <v/>
+      </c>
+      <c r="D13" s="17">
+        <f>IF(D10&gt;0,in_chip_cost/(D10*8760),"never")</f>
+        <v/>
+      </c>
+      <c r="E13" s="17">
+        <f>IF(E10&gt;0,in_chip_cost/(E10*8760),"never")</f>
+        <v/>
+      </c>
+      <c r="F13" s="17">
+        <f>IF(F10&gt;0,in_chip_cost/(F10*8760),"never")</f>
+        <v/>
+      </c>
+      <c r="G13" s="17">
+        <f>IF(G10&gt;0,in_chip_cost/(G10*8760),"never")</f>
+        <v/>
+      </c>
+      <c r="H13" s="17">
+        <f>IF(H10&gt;0,in_chip_cost/(H10*8760),"never")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Payback, as disclosed by the company</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>years</t>
         </is>
       </c>
-      <c r="C7" s="14">
+      <c r="C14" s="17">
         <f>in_disclosed_cash_payback_years</f>
         <v/>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Payback gap, model less disclosed</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="C8" s="15">
-        <f>C6-C7</f>
+      <c r="D14" s="17">
+        <f>in_disclosed_cash_payback_years</f>
+        <v/>
+      </c>
+      <c r="E14" s="17">
+        <f>in_disclosed_cash_payback_years</f>
+        <v/>
+      </c>
+      <c r="F14" s="17">
+        <f>in_disclosed_cash_payback_years</f>
+        <v/>
+      </c>
+      <c r="G14" s="17">
+        <f>in_disclosed_cash_payback_years</f>
+        <v/>
+      </c>
+      <c r="H14" s="17">
+        <f>in_disclosed_cash_payback_years</f>
         <v/>
       </c>
     </row>
